--- a/data/siembra.xlsx
+++ b/data/siembra.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcosfernandez/Library/CloudStorage/Dropbox/2026/app_info_lotes/la_alicia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13056E58-6CB5-D545-BAAD-9F2124BD5AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0907842-E0C5-1640-9A3C-34307D05861B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="51">
   <si>
     <t>Campo</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>267-26</t>
+  </si>
+  <si>
+    <t>B802</t>
+  </si>
+  <si>
+    <t>no aun</t>
   </si>
 </sst>
 </file>
@@ -983,7 +989,7 @@
         <v>41.1</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -997,7 +1003,7 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>90</v>
@@ -1012,13 +1018,13 @@
         <v>47</v>
       </c>
       <c r="J14">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K14">
-        <v>41.1</v>
+        <v>43.9</v>
       </c>
       <c r="L14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1053,7 +1059,7 @@
         <v>41.1</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1088,7 +1094,7 @@
         <v>41.1</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
